--- a/data/leave_records.xlsx
+++ b/data/leave_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Employee ID</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Approved</t>
-  </si>
-  <si>
-    <t>Pending</t>
   </si>
   <si>
     <t>You can go ahead</t>
@@ -520,10 +517,10 @@
         <v>23</v>
       </c>
       <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -552,7 +549,7 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -581,10 +578,10 @@
         <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -610,7 +607,10 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -636,7 +636,10 @@
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/leave_records.xlsx
+++ b/data/leave_records.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>Employee ID</t>
   </si>
@@ -49,62 +54,74 @@
     <t>D0355</t>
   </si>
   <si>
+    <t>INNONCENT MILANZI</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Annual leave</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>You can go ahead</t>
+  </si>
+  <si>
+    <t>Edward Ngozo</t>
+  </si>
+  <si>
     <t>C0077</t>
   </si>
   <si>
+    <t>Haricot Itimu</t>
+  </si>
+  <si>
+    <t>Peter Sibale</t>
+  </si>
+  <si>
     <t>C0176</t>
   </si>
   <si>
+    <t xml:space="preserve">Cedric January </t>
+  </si>
+  <si>
+    <t>Sick</t>
+  </si>
+  <si>
+    <t>Medical check</t>
+  </si>
+  <si>
     <t>CC0009</t>
   </si>
   <si>
-    <t>INNONCENT MILANZI</t>
-  </si>
-  <si>
-    <t>Haricot Itimu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cedric January </t>
-  </si>
-  <si>
     <t>Titus Demester</t>
   </si>
   <si>
-    <t>Annual</t>
-  </si>
-  <si>
-    <t>Sick</t>
-  </si>
-  <si>
-    <t>Annual leave</t>
-  </si>
-  <si>
-    <t>Medical check</t>
-  </si>
-  <si>
     <t>Want the medicine 💊 to take ifect</t>
   </si>
   <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>You can go ahead</t>
-  </si>
-  <si>
-    <t>Edward Ngozo</t>
-  </si>
-  <si>
-    <t>Peter Sibale</t>
+    <t>CC0003</t>
+  </si>
+  <si>
+    <t>Charles Byson Gama</t>
+  </si>
+  <si>
+    <t>Noted</t>
+  </si>
+  <si>
+    <t>Still under pressure at Agric. We need your assistance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,10 +132,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,13 +175,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -455,11 +477,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,15 +516,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2">
         <v>45824</v>
@@ -511,27 +536,27 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
         <v>45818</v>
@@ -543,24 +568,24 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2">
         <v>45819</v>
@@ -572,27 +597,27 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2">
         <v>45833</v>
@@ -604,24 +629,24 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
       </c>
       <c r="D6" s="2">
         <v>45833</v>
@@ -633,16 +658,80 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46107</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46107</v>
+      </c>
+      <c r="F8">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/leave_records.xlsx
+++ b/data/leave_records.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,11 +826,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>You can go ahead</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Peter Sibale</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -864,11 +872,65 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Still under pressure at Agric. We need your assistance</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Peter Sibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C0080</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peter Angumbwike Sibale</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Annual leave</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Go ahead</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Felix Lungu</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/leave_records.xlsx
+++ b/data/leave_records.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D0355</t>
+          <t>C0077</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INNONCENT MILANZI</t>
+          <t>Haricot Itimu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45824</v>
+        <v>45818</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45834</v>
+        <v>45838</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -519,26 +519,22 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>You can go ahead</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Edward Ngozo</t>
+          <t>Peter Sibale</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C0077</t>
+          <t>CC0003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Haricot Itimu</t>
+          <t>Charles Byson Gama</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,13 +543,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45818</v>
+        <v>46091</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45838</v>
+        <v>46107</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -565,7 +561,11 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Peter Sibale</t>
@@ -585,21 +585,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sick</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45819</v>
+        <v>46091</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45821</v>
+        <v>46107</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Medical check</t>
+          <t>Annual leave</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>You can go ahead</t>
+          <t>Still under pressure at Agric. We need your assistance</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -621,31 +621,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC0009</t>
+          <t>CC0006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Titus Demester</t>
+          <t>Samuel Chimulu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sick</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45833</v>
+        <v>46097</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45835</v>
+        <v>46112</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Want the medicine 💊 to take ifect</t>
+          <t>Annual leave</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -653,7 +653,11 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>You can go ahead</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Peter Sibale</t>
@@ -663,39 +667,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC0009</t>
+          <t>SG0055</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Titus Demester</t>
+          <t>Joyce Maxwell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sick</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45833</v>
+        <v>46099</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45835</v>
+        <v>46116</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Want the medicine 💊 to take ifect</t>
+          <t>Want to harvest Maize</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Still under pressure at Agric. We need your assistance</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Peter Sibale</t>
@@ -705,12 +713,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC0003</t>
+          <t>D0355</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Byson Gama</t>
+          <t>Innocent Milanzi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46091</v>
+        <v>46119</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46107</v>
+        <v>46136</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -734,203 +742,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Noted</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Peter Sibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>C0176</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cedric January </t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46091</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>46107</v>
-      </c>
-      <c r="F8" t="n">
-        <v>17</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Annual leave</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Still under pressure at Agric. We need your assistance</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Peter Sibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CC0006</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Samuel Chimulu</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Annual leave</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>You can go ahead</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Peter Sibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SG0055</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Joyce Maxwell</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>46116</v>
-      </c>
-      <c r="F10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Want to harvest Maize</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Still under pressure at Agric. We need your assistance</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Peter Sibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C0080</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Peter Angumbwike Sibale</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F11" t="n">
-        <v>25</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Annual leave</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Go ahead</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Felix Lungu</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
